--- a/REPL.xlsx
+++ b/REPL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75226B03-9531-4E09-9712-FAC415945205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD93322-CCF9-4F54-9F0C-430200095010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="6700" windowWidth="28800" windowHeight="15050" activeTab="1" xr2:uid="{B03E64F7-0E48-46C0-A539-9277124F6AAF}"/>
+    <workbookView xWindow="12710" yWindow="3380" windowWidth="22360" windowHeight="16580" xr2:uid="{B03E64F7-0E48-46C0-A539-9277124F6AAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>Price</t>
   </si>
@@ -90,15 +90,9 @@
     <t>Clinical Trials</t>
   </si>
   <si>
-    <t>2H2024: File IGNYTE</t>
-  </si>
-  <si>
     <t>Phase III "IGNYTE-3" with nivo vs BAT</t>
   </si>
   <si>
-    <t>Q125</t>
-  </si>
-  <si>
     <t>CMO</t>
   </si>
   <si>
@@ -109,6 +103,9 @@
   </si>
   <si>
     <t>Phase II "IGYNTE" PD-1 failed melanoma - NCT03767348</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -600,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03CECAEB-CD01-40D1-A1E9-0F2409DA5685}">
-  <dimension ref="B2:L12"/>
+  <dimension ref="B2:L10"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.81640625" customWidth="1"/>
@@ -623,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>12.71</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
@@ -638,10 +635,10 @@
         <v>1</v>
       </c>
       <c r="K3" s="3">
-        <v>77.086749999999995</v>
+        <v>83.945160999999999</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
@@ -652,7 +649,7 @@
       </c>
       <c r="K4" s="3">
         <f>+K2*K3</f>
-        <v>979.77259249999997</v>
+        <v>967.8877063299999</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
@@ -662,11 +659,11 @@
         <v>3</v>
       </c>
       <c r="K5" s="3">
-        <f>111.119+372.685</f>
-        <v>483.80399999999997</v>
+        <f>209.024+59.865</f>
+        <v>268.88900000000001</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
@@ -676,10 +673,10 @@
         <v>4</v>
       </c>
       <c r="K6" s="3">
-        <v>46.377000000000002</v>
+        <v>83.308000000000007</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
@@ -690,7 +687,7 @@
       </c>
       <c r="K7" s="3">
         <f>+K4-K5+K6</f>
-        <v>542.34559249999995</v>
+        <v>782.30670632999988</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
@@ -716,15 +713,10 @@
       <c r="G10" s="7"/>
       <c r="H10" s="8"/>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="G12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -780,17 +772,17 @@
     </row>
     <row r="6" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C6" s="14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C10" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
